--- a/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 32,83</t>
+          <t>-11,2; 29,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 79,84</t>
+          <t>-3,85; 75,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 25,19</t>
+          <t>-31,26; 23,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 16,92</t>
+          <t>-32,16; 15,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 18,01</t>
+          <t>-14,3; 18,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 48,24</t>
+          <t>-6,15; 51,2</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 535,97</t>
+          <t>-57,61; 537,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 2300,79</t>
+          <t>-37,11; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 265,44</t>
+          <t>-100,0; 256,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-87,14; 161,69</t>
+          <t>-87,55; 141,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 139,43</t>
+          <t>-59,7; 156,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 542,75</t>
+          <t>-35,63; 466,62</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 13,54</t>
+          <t>-4,99; 12,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 9,28</t>
+          <t>-10,26; 10,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 16,77</t>
+          <t>-2,13; 16,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 17,11</t>
+          <t>-4,09; 16,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 12,22</t>
+          <t>-1,25; 11,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 10,17</t>
+          <t>-4,22; 10,9</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 151,95</t>
+          <t>-30,45; 130,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,08; 90,18</t>
+          <t>-56,69; 104,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 168,8</t>
+          <t>-13,24; 153,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 157,35</t>
+          <t>-22,8; 163,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 110,59</t>
+          <t>-8,19; 108,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 84,84</t>
+          <t>-23,43; 94,22</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 18,29</t>
+          <t>-6,16; 18,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 21,51</t>
+          <t>-1,78; 22,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 20,85</t>
+          <t>-9,15; 21,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 14,82</t>
+          <t>-12,12; 14,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 14,98</t>
+          <t>-4,84; 15,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 15,4</t>
+          <t>-4,26; 14,93</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 581,78</t>
+          <t>-59,58; 690,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 880,58</t>
+          <t>-27,99; 812,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,41; 339,78</t>
+          <t>-54,1; 307,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 231,01</t>
+          <t>-67,1; 271,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 230,77</t>
+          <t>-37,81; 240,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 239,15</t>
+          <t>-31,89; 239,97</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 11,83</t>
+          <t>-0,93; 12,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 15,75</t>
+          <t>-2,44; 16,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 13,49</t>
+          <t>-2,54; 12,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 11,53</t>
+          <t>-4,58; 10,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 10,12</t>
+          <t>-0,1; 10,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,9</t>
+          <t>-1,95; 10,57</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 132,68</t>
+          <t>-7,41; 143,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 167,95</t>
+          <t>-18,97; 175,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 121,69</t>
+          <t>-14,46; 109,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 99,37</t>
+          <t>-24,46; 87,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 87,15</t>
+          <t>-0,24; 89,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 92,75</t>
+          <t>-10,18; 87,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 29,56</t>
+          <t>-10,19; 31,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 75,47</t>
+          <t>-3,39; 72,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 23,27</t>
+          <t>-32,92; 21,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 15,94</t>
+          <t>-31,82; 18,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 18,5</t>
+          <t>-14,02; 20,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 51,2</t>
+          <t>-6,62; 48,76</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 537,01</t>
+          <t>-63,71; 649,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,11; —</t>
+          <t>-33,93; 2093,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 256,53</t>
+          <t>-100,0; 220,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-87,55; 141,11</t>
+          <t>-84,41; 189,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 156,84</t>
+          <t>-62,03; 177,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 466,62</t>
+          <t>-39,36; 402,73</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 12,87</t>
+          <t>-4,56; 12,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 10,19</t>
+          <t>-10,33; 9,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 16,6</t>
+          <t>-1,81; 16,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 16,59</t>
+          <t>-2,42; 17,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 11,77</t>
+          <t>-0,42; 12,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 10,9</t>
+          <t>-3,18; 10,53</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 130,98</t>
+          <t>-28,73; 149,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 104,4</t>
+          <t>-57,4; 96,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 153,62</t>
+          <t>-12,74; 157,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 163,81</t>
+          <t>-16,81; 172,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 108,56</t>
+          <t>-3,03; 116,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 94,22</t>
+          <t>-19,4; 96,85</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 18,27</t>
+          <t>-6,31; 18,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 22,11</t>
+          <t>-1,2; 22,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 21,85</t>
+          <t>-10,7; 20,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 14,73</t>
+          <t>-14,29; 14,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 15,52</t>
+          <t>-3,09; 15,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 14,93</t>
+          <t>-3,04; 15,01</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 690,16</t>
+          <t>-64,29; 672,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 812,7</t>
+          <t>-23,33; 907,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 307,19</t>
+          <t>-59,39; 261,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 271,71</t>
+          <t>-70,63; 233,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 240,28</t>
+          <t>-24,84; 250,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 239,97</t>
+          <t>-24,9; 227,99</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,88</t>
+          <t>-1,63; 12,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 16,88</t>
+          <t>-2,55; 15,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 12,61</t>
+          <t>-2,05; 13,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,36</t>
+          <t>-3,81; 11,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 10,03</t>
+          <t>-0,4; 10,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 10,57</t>
+          <t>-1,22; 10,97</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 143,36</t>
+          <t>-11,62; 132,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 175,55</t>
+          <t>-19,55; 155,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 109,24</t>
+          <t>-12,69; 108,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 87,97</t>
+          <t>-20,72; 102,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 89,39</t>
+          <t>-3,15; 86,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 87,63</t>
+          <t>-7,33; 97,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-8,63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>8,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36,22</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,34</t>
+          <t>10,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>2,21</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 31,26</t>
+          <t>-30,21; 25,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 72,65</t>
+          <t>-30,39; 19,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 21,05</t>
+          <t>-10,48; 32,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 18,79</t>
+          <t>-10,39; 37,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 20,15</t>
+          <t>-14,87; 18,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 48,76</t>
+          <t>-13,61; 21,61</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-35,11%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-25,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>55,83%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>252,87%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-35,11%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-29,87%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 649,87</t>
+          <t>-100,0; 265,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 2093,7</t>
+          <t>-86,03; 221,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,2</t>
+          <t>-59,12; 535,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-84,41; 189,23</t>
+          <t>-60,51; 691,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 177,44</t>
+          <t>-61,57; 139,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 402,73</t>
+          <t>-58,48; 201,4</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,62</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>3,97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,23</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>5,67</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>5,64</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 12,43</t>
+          <t>-2,41; 16,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 9,67</t>
+          <t>-3,37; 18,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 16,1</t>
+          <t>-4,99; 13,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 17,43</t>
+          <t>-3,17; 14,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 12,43</t>
+          <t>-0,84; 12,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 10,53</t>
+          <t>-0,76; 13,26</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>29,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 149,86</t>
+          <t>-13,76; 168,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 96,38</t>
+          <t>-22,85; 161,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 157,47</t>
+          <t>-31,49; 151,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 172,84</t>
+          <t>-20,7; 167,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 116,47</t>
+          <t>-5,91; 110,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 96,85</t>
+          <t>-5,4; 115,31</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,69</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>5,6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,69</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>11,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>6,19</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 18,88</t>
+          <t>-11,08; 20,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 22,58</t>
+          <t>-12,13; 16,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 20,08</t>
+          <t>-6,71; 18,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 14,29</t>
+          <t>-0,68; 22,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 15,49</t>
+          <t>-4,14; 14,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 15,01</t>
+          <t>-2,78; 16,63</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>71,95%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>135,79%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>148,16%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 672,35</t>
+          <t>-61,41; 339,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 907,99</t>
+          <t>-68,72; 249,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 261,47</t>
+          <t>-68,68; 581,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,63; 233,18</t>
+          <t>-20,79; 926,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 250,06</t>
+          <t>-33,11; 230,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 227,99</t>
+          <t>-22,53; 250,17</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>4,92</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>7,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>5,18</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 12,02</t>
+          <t>-2,63; 13,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 15,77</t>
+          <t>-4,24; 12,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 13,37</t>
+          <t>-1,99; 11,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,73</t>
+          <t>0,18; 14,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 10,16</t>
+          <t>-0,06; 10,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 10,97</t>
+          <t>0,35; 10,25</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>40,69%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>52,49%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 132,4</t>
+          <t>-14,01; 121,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 155,84</t>
+          <t>-25,18; 102,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 108,96</t>
+          <t>-13,87; 132,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 102,43</t>
+          <t>-0,41; 162,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 86,3</t>
+          <t>1,52; 87,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 97,83</t>
+          <t>2,87; 89,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -63,6 +66,13 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -118,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,6 +524,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,50 +542,68 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2016/2012</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2023/2012</t>
+          <t>2016/2007</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2016/2012</t>
+          <t>2023/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023/2012</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2012</t>
+          <t>2016/2007</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2012</t>
+          <t>2023/2007</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012/2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -579,6 +616,9 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -591,467 +631,387 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.328896721577587</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5058204783286967</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.93113846558599</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.520391722193983</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.899058930820982</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>5.277580536950553</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>3.415400942184388</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>3.080687723620307</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4.078975119841413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-30,21; 25,19</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-30,39; 19,44</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,48; 32,83</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-10,39; 37,05</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,87; 18,01</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-13,61; 21,61</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.5931806776676813</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.337338449696254</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.885589004955725</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.359874952738134</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>2.263638376651387</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.616893849742742</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.048768490951614</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.8756729357707269</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.082234726367891</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-35,11%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-25,92%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>55,83%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>72,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.394272831542441</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.519235850164042</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.750099044157732</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.178937542961734</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>13.43469859585758</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>13.07610205468073</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>6.505581608345611</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6.904344941541122</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8.604527849739242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 265,44</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-86,03; 221,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-59,12; 535,97</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-60,51; 691,03</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-61,57; 139,43</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-58,48; 201,4</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2.166389565523702</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.3291793942349124</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1.90753523405837</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4.548325494164624</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>4.102584367134532</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>5.43201423249953</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,62</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,59</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.6986803856489626</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="n">
+        <v>0.1305725600354203</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.03693652142776861</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0.05532310056545275</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 16,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,37; 18,39</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,99; 13,54</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,17; 14,74</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,84; 12,22</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 13,26</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>39,34%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2.6130745718567</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.491379247867578</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.244203812162379</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.389146078444357</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2.875515209350362</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3.913826612349118</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2.504813522444118</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>3.18555595416776</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>4.085679844799843</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-13,76; 168,8</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-22,85; 161,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-31,49; 151,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-20,7; 167,85</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,91; 110,59</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-5,4; 115,31</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.402917970342398</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2.143994909005764</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.599722394964434</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.292727132085774</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.664691996305716</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2.560136814126835</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.730688600903608</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2.248965111538022</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>2.902853413837351</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,69</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,54</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.124058713232354</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.166260029662278</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.609692092065355</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.858747941681447</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.380163614955192</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.84998540789218</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>3.567986812392645</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>4.177447000134206</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5.775539020209356</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-11,08; 20,85</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,13; 16,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,71; 18,29</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 22,75</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 14,98</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-2,78; 16,63</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>9.398825559455444</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>12.55795179595421</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>15.26574545515021</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>15.48579134209484</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>18.63830300490224</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>25.36835349450061</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>11.36640489024916</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>14.45549477083781</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>18.54009927358233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>71,95%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>148,16%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,97%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1.434542528395911</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1.922707069865538</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>3.174273261872659</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="n">
+        <v>3.043461019998821</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>4.156338261230262</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>4.932565589325152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-61,41; 339,78</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-68,72; 249,78</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-68,68; 581,78</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-20,79; 926,84</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-33,11; 230,77</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-22,53; 250,17</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="n">
+        <v>47.54433478786103</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>61.10041724768453</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>66.58884658233539</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +1019,395 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,92</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,37</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,94</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>3.004766089401546</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.784618391958194</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.725592760924826</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.677174766417926</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.23238129778804</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5.222182548079974</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2.346998530606379</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>2.51983935632341</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4.430544473398445</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 13,49</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,24; 12,08</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,99; 11,83</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 14,64</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,06; 10,12</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,35; 10,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.191195708247865</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.207579669478475</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.673286747722083</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.4327815432033646</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.9502291069874772</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>2.71534120709983</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.038008049176443</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1.370827400954572</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>2.638265859002597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>20,91%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>37,86%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.780204567701326</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.625440266852141</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.134141911182004</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.292669336488036</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.566682012623927</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8.614743293690694</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>4.018222612571727</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>4.156573998207412</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7.039243236713455</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-14,01; 121,69</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-25,18; 102,9</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-13,87; 132,68</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-0,41; 162,65</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 87,15</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 89,77</t>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.772585564812329</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2.993903801181958</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>3.957684192004163</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2.372641223080962</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2.981897206483106</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>4.338147090320123</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>2.5776520156067</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>2.987895121572931</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>4.141003422906244</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1.866363706494165</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.929961767866677</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>2.685085558627047</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1.560739734183593</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>2.025056248817363</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>3.198971625286932</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1.903832315505883</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>2.276130729467257</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>3.274648276028485</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4.170474849782424</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.25386404553704</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>6.348079031132957</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.420031793467344</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>4.200252123229738</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>6.031595008613277</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>3.30606858415569</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>3.793086074555008</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5.694123015511763</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>7.523622344544407</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>8.124186254830221</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>10.73947783524155</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>25.17089334421009</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>31.6343726213776</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>46.02256618476406</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>10.95046453178118</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>12.69327254236269</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>17.59194446494991</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2.192639882910503</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>2.314517727703302</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>3.504460182152967</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="n">
+        <v>4.434189098726384</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>5.09780972340234</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>7.234901392512908</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>31.47138086943155</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>34.81137885693973</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>43.6066114529976</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="n">
+        <v>45.84983098855331</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>37.16673669875112</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>57.57961404921287</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1415,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
